--- a/src/main/resources/client-labels/apc-etiquetas-korea.xlsx
+++ b/src/main/resources/client-labels/apc-etiquetas-korea.xlsx
@@ -3,19 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\documentos\ETIQUETAS\APC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\system.PUNTOTRES\Documents\WORKSPACE\PackingListAutomation\target\muestras-etiquetas-apc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1510D8-A0DD-4BAB-8C99-FBA6943C6303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48970918-DD1B-42F1-85A1-436E9C8212ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Etiquette colis FC Logistique" sheetId="5" r:id="rId1"/>
     <sheet name="Etiquette Palette FC logistique" sheetId="6" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Etiquette colis FC Logistique'!$A$1:$D$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Etiquette Palette FC logistique'!$A$1:$D$26</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="33">
   <si>
     <r>
       <t xml:space="preserve">DESTINATAIRE
@@ -185,25 +189,47 @@
     <t>U</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>PUN20260717KRT1</t>
-  </si>
-  <si>
-    <t>LAW-GRIS ARDOISE</t>
-  </si>
-  <si>
     <t>PXCBC-F67008</t>
   </si>
   <si>
-    <t>7,60 KG</t>
-  </si>
-  <si>
-    <t>11 / 11</t>
-  </si>
-  <si>
-    <t>88,48 Kg</t>
+    <t>DESTINATAIRE
+(Consignee)</t>
+  </si>
+  <si>
+    <t>DESTINATION
+(Destination)</t>
+  </si>
+  <si>
+    <t>4100128863</t>
+  </si>
+  <si>
+    <t>PUN20260928WH1</t>
+  </si>
+  <si>
+    <t>LZZ-NOIR</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1 / 3</t>
+  </si>
+  <si>
+    <t>7,60 Kg</t>
+  </si>
+  <si>
+    <t>Nombre total de colis sur la palette
+(Total number of packages on the palette)</t>
+  </si>
+  <si>
+    <t>Poids brut 
+(Total gross weight)</t>
+  </si>
+  <si>
+    <t>25,20 Kg</t>
+  </si>
+  <si>
+    <t>16,20 Kg</t>
   </si>
 </sst>
 </file>
@@ -466,15 +492,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2893219</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
+      <xdr:colOff>2806628</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>103909</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1059656</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>106615</xdr:rowOff>
+      <xdr:colOff>973065</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>20024</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -504,8 +530,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3167063" y="214313"/>
-          <a:ext cx="2214562" cy="654302"/>
+          <a:off x="3256901" y="103909"/>
+          <a:ext cx="2218891" cy="608842"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -528,14 +554,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>2893219</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>23813</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1059656</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>106615</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>227842</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -565,8 +591,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3163094" y="214313"/>
-          <a:ext cx="2214562" cy="654302"/>
+          <a:off x="4122810" y="9912495"/>
+          <a:ext cx="2218891" cy="654302"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -593,15 +619,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2657475</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>2641600</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1033462</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>63752</xdr:rowOff>
+      <xdr:colOff>1017587</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>111377</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -631,8 +657,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2933700" y="171450"/>
-          <a:ext cx="2214562" cy="654302"/>
+          <a:off x="3165475" y="238125"/>
+          <a:ext cx="2106612" cy="444752"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -945,245 +971,209 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B6:C43"/>
+  <dimension ref="B2:C36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="3" width="60.7109375" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" customWidth="1"/>
-    <col min="5" max="6" width="60.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="6.7109375"/>
+    <col min="2" max="3" customWidth="true" width="60.7109375"/>
+    <col min="4" max="4" customWidth="true" width="6.7109375"/>
+    <col min="5" max="6" customWidth="true" width="60.7109375"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:3" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-    </row>
-    <row r="8" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:3" ht="124.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+    <row r="2" spans="2:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+    </row>
+    <row r="3" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:3" ht="124.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
+    <row r="6" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="7" t="s">
+    <row r="7" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C7" s="14" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
     <row r="12" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="15"/>
+    </row>
+    <row r="17" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+    </row>
+    <row r="22" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+    </row>
+    <row r="23" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:3" ht="124.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="3">
-        <v>4100128690</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="10" t="s">
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="7" t="s">
+      <c r="C32" s="16"/>
+    </row>
+    <row r="33" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C33" s="14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="11" t="s">
+    <row r="34" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="11" t="s">
+      <c r="C35" s="15"/>
+    </row>
+    <row r="36" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-    </row>
-    <row r="29" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-    </row>
-    <row r="30" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="2:3" ht="124.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="3">
-        <v>4100128690</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="2"/>
-    </row>
-    <row r="42" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="C36" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="59" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1194,80 +1184,74 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C14"/>
+  <dimension ref="B4:C13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="2" max="3" width="57.5703125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="7.85546875"/>
+    <col min="2" max="3" customWidth="true" width="56.0"/>
+    <col min="4" max="4" customWidth="true" width="7.85546875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C1">
+    <row r="4" spans="2:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+    </row>
+    <row r="5" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:3" ht="124.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:3" ht="124.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="102" thickBot="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="2:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
+    <row r="10" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="2:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="13" t="s">
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="2:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B6:C6"/>
+  <mergeCells count="2">
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="76" fitToWidth="0" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>